--- a/datos_iniciales/lista de insumos gastronomia.xlsx
+++ b/datos_iniciales/lista de insumos gastronomia.xlsx
@@ -4278,47 +4278,47 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4330,35 +4330,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4366,7 +4366,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4374,7 +4374,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4382,19 +4382,19 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4402,23 +4402,23 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -4426,15 +4426,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4442,7 +4442,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4450,15 +4450,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4470,7 +4470,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4478,7 +4478,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4486,19 +4486,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4510,23 +4510,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="23" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -4534,19 +4534,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4562,7 +4562,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4574,11 +4574,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4902,10 +4902,10 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="B1:T883"/>
-  <sheetFormatPr defaultColWidth="11.4453125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="19.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.34"/>
